--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_44.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4960506.90970411</v>
+        <v>4920480.816950712</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.318645787</v>
+        <v>6767152.318645786</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.318645787</v>
+        <v>6767152.318645786</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517474</v>
+        <v>2916902.906517487</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517474</v>
+        <v>2916902.906517487</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42797442.66179451</v>
+        <v>42797442.66179449</v>
       </c>
     </row>
   </sheetData>
@@ -657,7 +657,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>449.4745782429939</v>
       </c>
       <c r="D2" t="n">
         <v>10.33915573984979</v>
@@ -675,13 +675,13 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>418.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>313.1545016101228</v>
+        <v>97.12488247690061</v>
       </c>
       <c r="L2" t="n">
         <v>814</v>
@@ -690,7 +690,7 @@
         <v>297.9910820919849</v>
       </c>
       <c r="N2" t="n">
-        <v>194.5855355810472</v>
+        <v>410.6151547142695</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -702,13 +702,13 @@
         <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>337.538960359443</v>
       </c>
       <c r="T2" t="n">
-        <v>530.163813431294</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -723,7 +723,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -781,13 +781,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>147.2737972923793</v>
+        <v>243.8995092302829</v>
       </c>
       <c r="S3" t="n">
         <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>63.08338960093648</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
         <v>0.2103597601867477</v>
@@ -796,7 +796,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>419.8627394453875</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>114.9691617060968</v>
+        <v>114.9691617061033</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E5" t="n">
-        <v>347.8515213095984</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
         <v>4.889628708011855</v>
@@ -909,16 +909,16 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>8.009658703527407</v>
+        <v>100.6192915779626</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>634.7678887921559</v>
+        <v>731.8927712690562</v>
       </c>
       <c r="K5" t="n">
-        <v>97.12488247690055</v>
+        <v>814</v>
       </c>
       <c r="L5" t="n">
         <v>814</v>
@@ -933,22 +933,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>370.9706110579117</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
       </c>
       <c r="U5" t="n">
-        <v>649.2212965486107</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -960,7 +960,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -976,7 +976,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1024,7 +1024,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>5.357765217513816</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>148.6880250402008</v>
+        <v>96.62571193790347</v>
       </c>
     </row>
     <row r="7">
@@ -1094,10 +1094,10 @@
         <v>287.4478973282775</v>
       </c>
       <c r="Q7" t="n">
-        <v>296.6291885713621</v>
+        <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>326.6021279811511</v>
+        <v>297.3920501269228</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>142.0842111174291</v>
+        <v>449.4745782429939</v>
       </c>
       <c r="D8" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E8" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F8" t="n">
         <v>4.889628708011855</v>
@@ -1146,7 +1146,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>8.009658703527407</v>
+        <v>351.4978904062571</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -1155,31 +1155,31 @@
         <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
+        <v>97.12488247690067</v>
+      </c>
+      <c r="L8" t="n">
         <v>814</v>
       </c>
-      <c r="L8" t="n">
-        <v>611.1455837021026</v>
-      </c>
       <c r="M8" t="n">
-        <v>814.0000000000045</v>
+        <v>297.9910820919849</v>
       </c>
       <c r="N8" t="n">
         <v>194.5855355810472</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>216.0296191332261</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q8" t="n">
-        <v>370.9706110579162</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
@@ -1197,7 +1197,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1210,10 +1210,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>97.2343191717691</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1267,16 +1267,16 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>77.58836382881032</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>114.9691617061082</v>
+        <v>114.9691617060977</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
@@ -1371,16 +1371,16 @@
         <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>124.0498976023938</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1413,10 +1413,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>109.8006938722124</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
@@ -1428,7 +1428,7 @@
         <v>404.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X11" t="n">
         <v>367.2818334606677</v>
@@ -1562,16 +1562,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>70.69971198282684</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>153.8896287080119</v>
+        <v>71.22605108397006</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>53.74128073011011</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>53.74128073011011</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>125.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>124.7573722870162</v>
+        <v>124.3267636724302</v>
       </c>
       <c r="H17" t="n">
         <v>129.0096587035274</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>215.4175591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T17" t="n">
         <v>307.6755817285639</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>338.6387678008247</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>447.6021279811511</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>202.5687043409885</v>
+        <v>202.9993129555745</v>
       </c>
       <c r="C20" t="n">
         <v>170.4745782429939</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>215.8481678023229</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T20" t="n">
         <v>307.6755817285639</v>
@@ -2276,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>338.6387678008247</v>
+        <v>377.7929984536983</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>170.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>131.3391557398498</v>
+        <v>130.9085471252638</v>
       </c>
       <c r="E23" t="n">
         <v>125.3632896068686</v>
@@ -2331,7 +2331,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>128.5790500890098</v>
+        <v>129.0096587035274</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="Q25" t="n">
-        <v>338.6387678008247</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2553,22 +2553,22 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>189.411675845388</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,16 +2601,16 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S26" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>361.6755817285639</v>
+        <v>274.8423949628424</v>
       </c>
       <c r="U26" t="n">
         <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>413.3734759809475</v>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>25.7120484382364</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D28" t="n">
         <v>60.53621805555548</v>
@@ -2720,10 +2720,10 @@
         <v>55.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1.165447329623562</v>
       </c>
       <c r="H28" t="n">
         <v>3.77112610161862</v>
@@ -2735,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L28" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -2790,13 +2790,13 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>189.411675845388</v>
+        <v>10.04838623851932</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2987,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="Q31" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3045,34 +3045,34 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>8.45659138541424</v>
       </c>
       <c r="J32" t="n">
-        <v>757.6173000000412</v>
+        <v>377.7382696589747</v>
       </c>
       <c r="K32" t="n">
-        <v>743.147852151686</v>
+        <v>10.23281455315225</v>
       </c>
       <c r="L32" t="n">
-        <v>727.1079320760621</v>
+        <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>256.9910820920268</v>
+        <v>256.9910820920259</v>
       </c>
       <c r="N32" t="n">
-        <v>153.5855355810893</v>
+        <v>153.5855355810884</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>341.5828712849403</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="Q32" t="n">
-        <v>377.6514823270895</v>
+        <v>329.9706110579529</v>
       </c>
       <c r="R32" t="n">
-        <v>8.456591385414804</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>203.8481678023229</v>
@@ -3212,16 +3212,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>108.4418998849671</v>
+        <v>181.8647883058126</v>
       </c>
       <c r="P34" t="n">
         <v>396.4478973282775</v>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3285,31 +3285,31 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>377.7382696589829</v>
+        <v>377.738269658982</v>
       </c>
       <c r="K35" t="n">
-        <v>773</v>
+        <v>351.8156858377657</v>
       </c>
       <c r="L35" t="n">
-        <v>727.1079320759791</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>654.6988358539375</v>
+        <v>256.9910820920331</v>
       </c>
       <c r="N35" t="n">
-        <v>153.5855355810966</v>
+        <v>153.5855355810957</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="Q35" t="n">
-        <v>329.970611057961</v>
+        <v>329.9706110579601</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>8.456591385414804</v>
       </c>
       <c r="S35" t="n">
         <v>203.8481678023229</v>
@@ -3330,7 +3330,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>228.7740240682207</v>
+        <v>220.3174326828064</v>
       </c>
     </row>
     <row r="36">
@@ -3519,34 +3519,34 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>8.45659138541424</v>
       </c>
       <c r="J38" t="n">
-        <v>377.7382696589902</v>
+        <v>757.6173000000546</v>
       </c>
       <c r="K38" t="n">
-        <v>351.8156858378189</v>
+        <v>10.23281455308506</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>256.9910820920413</v>
+        <v>256.9910820920404</v>
       </c>
       <c r="N38" t="n">
-        <v>153.5855355811038</v>
+        <v>153.5855355811029</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>734.7038409438887</v>
       </c>
       <c r="P38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="Q38" t="n">
-        <v>329.9706110579683</v>
+        <v>329.9706110579674</v>
       </c>
       <c r="R38" t="n">
-        <v>8.456591385414804</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>203.8481678023229</v>
@@ -3698,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>70.05053078767355</v>
       </c>
       <c r="Q40" t="n">
         <v>434.839266425598</v>
@@ -3707,7 +3707,7 @@
         <v>435.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>70.05053078764668</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>268.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>236.4745782429939</v>
@@ -3747,13 +3747,13 @@
         <v>191.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>114.0878988228846</v>
+        <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>195.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>37.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>281.8481678023229</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>436.2212965486107</v>
       </c>
       <c r="V41" t="n">
-        <v>416.8510241668239</v>
+        <v>330.4527258514597</v>
       </c>
       <c r="W41" t="n">
         <v>425.3734759809475</v>
@@ -3865,7 +3865,7 @@
         <v>334.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>253.5639999646113</v>
+        <v>116.0975572222915</v>
       </c>
       <c r="T42" t="n">
         <v>192.3577652175138</v>
@@ -3877,7 +3877,7 @@
         <v>201.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>81.90670016750896</v>
+        <v>219.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>206.8627394453875</v>
@@ -3975,22 +3975,22 @@
         <v>294.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>262.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>217.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>217.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>216.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>85.59095627391456</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,19 +4020,19 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>63.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>307.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>340.6887307759347</v>
       </c>
       <c r="U44" t="n">
-        <v>462.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>442.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>451.3734759809475</v>
@@ -4041,7 +4041,7 @@
         <v>405.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>324.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>53.23386227040424</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
         <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>82.40921324489068</v>
       </c>
       <c r="X45" t="n">
         <v>232.8627394453875</v>
@@ -4190,10 +4190,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>12.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>39.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1106.448124213083</v>
+        <v>1358.891397260877</v>
       </c>
       <c r="C2" t="n">
-        <v>1056.473802755514</v>
+        <v>904.876671762903</v>
       </c>
       <c r="D2" t="n">
-        <v>1046.0302110991</v>
+        <v>894.4330801064891</v>
       </c>
       <c r="E2" t="n">
-        <v>637.5824438194345</v>
+        <v>485.9853128268238</v>
       </c>
       <c r="F2" t="n">
-        <v>632.6434249224528</v>
+        <v>481.0462939298421</v>
       </c>
       <c r="G2" t="n">
-        <v>224.8076953396081</v>
+        <v>73.21056434699739</v>
       </c>
       <c r="H2" t="n">
-        <v>216.7171309926107</v>
+        <v>65.12</v>
       </c>
       <c r="I2" t="n">
         <v>65.12</v>
@@ -4324,13 +4324,13 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K2" t="n">
-        <v>937.5543724554985</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L2" t="n">
-        <v>921.1921502332762</v>
+        <v>1139.40388673148</v>
       </c>
       <c r="M2" t="n">
-        <v>1426.051057211069</v>
+        <v>1644.262793709273</v>
       </c>
       <c r="N2" t="n">
         <v>2035.360011169607</v>
@@ -4345,28 +4345,28 @@
         <v>3256</v>
       </c>
       <c r="R2" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>3160.193769896644</v>
+        <v>2661.638829103295</v>
       </c>
       <c r="T2" t="n">
-        <v>2624.67476643069</v>
+        <v>2473.077635438079</v>
       </c>
       <c r="U2" t="n">
-        <v>2372.936083048255</v>
+        <v>2221.338952055644</v>
       </c>
       <c r="V2" t="n">
-        <v>2140.763331364595</v>
+        <v>1989.166200371984</v>
       </c>
       <c r="W2" t="n">
-        <v>1899.982042494951</v>
+        <v>1748.38491150234</v>
       </c>
       <c r="X2" t="n">
-        <v>1705.757968292256</v>
+        <v>1554.160837299645</v>
       </c>
       <c r="Y2" t="n">
-        <v>1189.275713057098</v>
+        <v>1441.718986104891</v>
       </c>
     </row>
     <row r="3">
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.12</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="C3" t="n">
         <v>65.12</v>
@@ -4424,28 +4424,28 @@
         <v>1220.552420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>1071.791008962092</v>
+        <v>974.1892797318862</v>
       </c>
       <c r="S3" t="n">
-        <v>1004.554645361474</v>
+        <v>906.9529161312688</v>
       </c>
       <c r="T3" t="n">
-        <v>940.8340498049729</v>
+        <v>901.5410320731741</v>
       </c>
       <c r="U3" t="n">
-        <v>940.6215651987236</v>
+        <v>901.3285474669248</v>
       </c>
       <c r="V3" t="n">
-        <v>925.9643256113295</v>
+        <v>886.6713078795307</v>
       </c>
       <c r="W3" t="n">
-        <v>489.2237772175632</v>
+        <v>853.9711635261685</v>
       </c>
       <c r="X3" t="n">
-        <v>65.12</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="Y3" t="n">
-        <v>65.12</v>
+        <v>429.8673863086054</v>
       </c>
     </row>
     <row r="4">
@@ -4455,37 +4455,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>648.7544645575567</v>
+        <v>741.9879361380738</v>
       </c>
       <c r="C4" t="n">
-        <v>774.7564703759925</v>
+        <v>867.9899419565096</v>
       </c>
       <c r="D4" t="n">
-        <v>774.7564703759925</v>
+        <v>981.3090860815097</v>
       </c>
       <c r="E4" t="n">
-        <v>892.5853745874056</v>
+        <v>1099.137990292923</v>
       </c>
       <c r="F4" t="n">
-        <v>1016.946347179341</v>
+        <v>1223.498962884858</v>
       </c>
       <c r="G4" t="n">
-        <v>1170.352913066226</v>
+        <v>1376.905528771744</v>
       </c>
       <c r="H4" t="n">
-        <v>1339.869498225624</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="I4" t="n">
-        <v>1339.869498225624</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="J4" t="n">
-        <v>1546.422113931135</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931135</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="L4" t="n">
-        <v>1546.422113931135</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="M4" t="n">
         <v>1430.29164756134</v>
@@ -4506,25 +4506,25 @@
         <v>65.12</v>
       </c>
       <c r="S4" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T4" t="n">
-        <v>290.445934252978</v>
+        <v>253.1956791588049</v>
       </c>
       <c r="U4" t="n">
-        <v>536.9971268912645</v>
+        <v>499.7468717970915</v>
       </c>
       <c r="V4" t="n">
-        <v>536.9971268912645</v>
+        <v>630.2305984717816</v>
       </c>
       <c r="W4" t="n">
-        <v>536.9971268912645</v>
+        <v>630.2305984717816</v>
       </c>
       <c r="X4" t="n">
-        <v>536.9971268912645</v>
+        <v>630.2305984717816</v>
       </c>
       <c r="Y4" t="n">
-        <v>536.9971268912645</v>
+        <v>630.2305984717816</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1049.365529973416</v>
+        <v>795.95280388423</v>
       </c>
       <c r="C5" t="n">
-        <v>595.3508044754427</v>
+        <v>745.9784824266603</v>
       </c>
       <c r="D5" t="n">
-        <v>584.9072128190288</v>
+        <v>331.4944867298423</v>
       </c>
       <c r="E5" t="n">
-        <v>233.5420397790304</v>
+        <v>327.0871234905811</v>
       </c>
       <c r="F5" t="n">
-        <v>228.6030208820488</v>
+        <v>322.1481045935994</v>
       </c>
       <c r="G5" t="n">
-        <v>224.8076953396081</v>
+        <v>318.3527790511588</v>
       </c>
       <c r="H5" t="n">
         <v>216.7171309926107</v>
@@ -4558,22 +4558,22 @@
         <v>65.12</v>
       </c>
       <c r="J5" t="n">
-        <v>229.8003143513577</v>
+        <v>131.6943724554988</v>
       </c>
       <c r="K5" t="n">
-        <v>937.5543724554985</v>
+        <v>115.3321502332764</v>
       </c>
       <c r="L5" t="n">
-        <v>921.1921502332762</v>
+        <v>98.96992801105404</v>
       </c>
       <c r="M5" t="n">
-        <v>1426.051057211069</v>
+        <v>603.828834988847</v>
       </c>
       <c r="N5" t="n">
-        <v>2035.360011169607</v>
+        <v>1213.137788947385</v>
       </c>
       <c r="O5" t="n">
-        <v>2841.220011169607</v>
+        <v>2018.997788947385</v>
       </c>
       <c r="P5" t="n">
         <v>2824.857788947385</v>
@@ -4582,28 +4582,28 @@
         <v>3256</v>
       </c>
       <c r="R5" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>3160.193769896644</v>
+        <v>2502.740639767053</v>
       </c>
       <c r="T5" t="n">
-        <v>2971.632576231427</v>
+        <v>2314.179446101837</v>
       </c>
       <c r="U5" t="n">
-        <v>2315.853488808588</v>
+        <v>2062.440762719402</v>
       </c>
       <c r="V5" t="n">
-        <v>2083.680737124928</v>
+        <v>1830.268011035741</v>
       </c>
       <c r="W5" t="n">
-        <v>1842.899448255284</v>
+        <v>1589.486722166097</v>
       </c>
       <c r="X5" t="n">
-        <v>1648.675374052589</v>
+        <v>1395.262647963403</v>
       </c>
       <c r="Y5" t="n">
-        <v>1536.233522857835</v>
+        <v>878.7803927282447</v>
       </c>
     </row>
     <row r="6">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>781.3195952961838</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="C6" t="n">
-        <v>416.5722089875784</v>
+        <v>65.12</v>
       </c>
       <c r="D6" t="n">
         <v>65.12</v>
@@ -4667,22 +4667,22 @@
         <v>1004.554645361474</v>
       </c>
       <c r="T6" t="n">
-        <v>999.1427613033796</v>
+        <v>595.1023572629756</v>
       </c>
       <c r="U6" t="n">
-        <v>998.9302766971304</v>
+        <v>594.8898726567263</v>
       </c>
       <c r="V6" t="n">
-        <v>984.2730371097363</v>
+        <v>580.2326330693322</v>
       </c>
       <c r="W6" t="n">
-        <v>951.5728927563741</v>
+        <v>547.5324887159701</v>
       </c>
       <c r="X6" t="n">
-        <v>931.509519579215</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="Y6" t="n">
-        <v>781.3195952961838</v>
+        <v>429.8673863086054</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>810.0297405151414</v>
+        <v>935.5162293528665</v>
       </c>
       <c r="C7" t="n">
-        <v>936.0317463335772</v>
+        <v>1061.518235171302</v>
       </c>
       <c r="D7" t="n">
-        <v>1049.350890458577</v>
+        <v>1061.518235171302</v>
       </c>
       <c r="E7" t="n">
-        <v>1167.17979466999</v>
+        <v>1061.518235171302</v>
       </c>
       <c r="F7" t="n">
-        <v>1291.540767261926</v>
+        <v>1061.518235171302</v>
       </c>
       <c r="G7" t="n">
-        <v>1291.540767261926</v>
+        <v>1214.924801058188</v>
       </c>
       <c r="H7" t="n">
-        <v>1291.540767261926</v>
+        <v>1214.924801058188</v>
       </c>
       <c r="I7" t="n">
-        <v>1436.057679994263</v>
+        <v>1436.057679994271</v>
       </c>
       <c r="J7" t="n">
-        <v>1436.057679994263</v>
+        <v>1436.057679994271</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931131</v>
+        <v>1546.422113931139</v>
       </c>
       <c r="L7" t="n">
-        <v>1522.636630943475</v>
+        <v>1522.636630943483</v>
       </c>
       <c r="M7" t="n">
-        <v>1400.786518415647</v>
+        <v>1400.786518415655</v>
       </c>
       <c r="N7" t="n">
-        <v>1227.872300969501</v>
+        <v>1227.872300969508</v>
       </c>
       <c r="O7" t="n">
-        <v>984.9979938189805</v>
+        <v>984.9979938189882</v>
       </c>
       <c r="P7" t="n">
-        <v>694.646582376276</v>
+        <v>694.6465823762837</v>
       </c>
       <c r="Q7" t="n">
-        <v>395.0211393749001</v>
+        <v>365.516010229215</v>
       </c>
       <c r="R7" t="n">
         <v>65.12</v>
       </c>
       <c r="S7" t="n">
-        <v>65.12</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="T7" t="n">
-        <v>65.12</v>
+        <v>290.445934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>65.12</v>
+        <v>453.0465805409511</v>
       </c>
       <c r="V7" t="n">
-        <v>263.941392885946</v>
+        <v>651.867973426897</v>
       </c>
       <c r="W7" t="n">
-        <v>435.8323111456234</v>
+        <v>823.7588916865744</v>
       </c>
       <c r="X7" t="n">
-        <v>586.8631021698169</v>
+        <v>823.7588916865744</v>
       </c>
       <c r="Y7" t="n">
-        <v>698.2724028488492</v>
+        <v>823.7588916865744</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>391.9123998438259</v>
+        <v>1857.446338054225</v>
       </c>
       <c r="C8" t="n">
-        <v>248.3929946747056</v>
+        <v>1403.431612556251</v>
       </c>
       <c r="D8" t="n">
-        <v>237.9494030182917</v>
+        <v>988.9476168594329</v>
       </c>
       <c r="E8" t="n">
-        <v>233.5420397790304</v>
+        <v>580.4998495797676</v>
       </c>
       <c r="F8" t="n">
-        <v>228.6030208820488</v>
+        <v>575.5608306827859</v>
       </c>
       <c r="G8" t="n">
-        <v>224.8076953396081</v>
+        <v>571.7655051403452</v>
       </c>
       <c r="H8" t="n">
         <v>216.7171309926107</v>
@@ -4798,49 +4798,49 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>431.6498286273397</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L8" t="n">
-        <v>620.1910572110743</v>
+        <v>1139.40388673148</v>
       </c>
       <c r="M8" t="n">
-        <v>603.8288349888475</v>
+        <v>1644.262793709273</v>
       </c>
       <c r="N8" t="n">
-        <v>1213.137788947386</v>
+        <v>2253.571747667811</v>
       </c>
       <c r="O8" t="n">
-        <v>2018.997788947386</v>
+        <v>2841.220011169603</v>
       </c>
       <c r="P8" t="n">
-        <v>2824.857788947386</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q8" t="n">
         <v>3256</v>
       </c>
       <c r="R8" t="n">
-        <v>3002.587273910814</v>
+        <v>3256</v>
       </c>
       <c r="S8" t="n">
-        <v>2502.740639767053</v>
+        <v>3160.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>2314.179446101837</v>
+        <v>2971.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>2062.440762719402</v>
+        <v>2719.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>1830.268011035741</v>
+        <v>2487.721141165332</v>
       </c>
       <c r="W8" t="n">
-        <v>1589.486722166097</v>
+        <v>2246.939852295688</v>
       </c>
       <c r="X8" t="n">
-        <v>1395.262647963403</v>
+        <v>2052.715778092993</v>
       </c>
       <c r="Y8" t="n">
-        <v>878.7803927282447</v>
+        <v>1940.273926898239</v>
       </c>
     </row>
     <row r="9">
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>528.0838703204934</v>
+        <v>65.12</v>
       </c>
       <c r="C9" t="n">
-        <v>163.336484011888</v>
+        <v>65.12</v>
       </c>
       <c r="D9" t="n">
         <v>65.12</v>
@@ -4910,16 +4910,16 @@
         <v>998.9302766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>984.2730371097363</v>
+        <v>580.2326330693322</v>
       </c>
       <c r="W9" t="n">
-        <v>951.5728927563741</v>
+        <v>143.492084675566</v>
       </c>
       <c r="X9" t="n">
-        <v>931.509519579215</v>
+        <v>65.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>528.0838703204934</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="10">
@@ -4929,37 +4929,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>406.5569367675253</v>
+        <v>1281.906867406406</v>
       </c>
       <c r="C10" t="n">
-        <v>406.5569367675253</v>
+        <v>1407.908873224841</v>
       </c>
       <c r="D10" t="n">
-        <v>406.5569367675253</v>
+        <v>1521.228017349842</v>
       </c>
       <c r="E10" t="n">
-        <v>406.5569367675253</v>
+        <v>1546.422113931136</v>
       </c>
       <c r="F10" t="n">
-        <v>530.9179093594607</v>
+        <v>1546.422113931136</v>
       </c>
       <c r="G10" t="n">
-        <v>684.324475246346</v>
+        <v>1546.422113931136</v>
       </c>
       <c r="H10" t="n">
-        <v>853.8410604057435</v>
+        <v>1546.422113931136</v>
       </c>
       <c r="I10" t="n">
-        <v>1074.973939341827</v>
+        <v>1546.422113931136</v>
       </c>
       <c r="J10" t="n">
-        <v>1436.057679994278</v>
+        <v>1546.422113931136</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.422113931146</v>
+        <v>1546.422113931136</v>
       </c>
       <c r="L10" t="n">
-        <v>1546.422113931146</v>
+        <v>1546.422113931136</v>
       </c>
       <c r="M10" t="n">
         <v>1430.29164756134</v>
@@ -4986,19 +4986,19 @@
         <v>290.445934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>406.5569367675253</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="V10" t="n">
-        <v>406.5569367675253</v>
+        <v>735.8185197772104</v>
       </c>
       <c r="W10" t="n">
-        <v>406.5569367675253</v>
+        <v>907.7094380368878</v>
       </c>
       <c r="X10" t="n">
-        <v>406.5569367675253</v>
+        <v>1058.740229061081</v>
       </c>
       <c r="Y10" t="n">
-        <v>406.5569367675253</v>
+        <v>1170.149529740114</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1022.518004631051</v>
+        <v>417.1649250963513</v>
       </c>
       <c r="C11" t="n">
-        <v>795.7760064058045</v>
+        <v>190.4229268711049</v>
       </c>
       <c r="D11" t="n">
-        <v>608.5647379817138</v>
+        <v>65.12</v>
       </c>
       <c r="E11" t="n">
-        <v>427.3896979747758</v>
+        <v>65.12</v>
       </c>
       <c r="F11" t="n">
-        <v>245.6830023101174</v>
+        <v>65.12</v>
       </c>
       <c r="G11" t="n">
         <v>65.12</v>
@@ -5056,28 +5056,28 @@
         <v>3256</v>
       </c>
       <c r="R11" t="n">
-        <v>3256</v>
+        <v>3229.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>3145.090208209886</v>
+        <v>2957.286094312508</v>
       </c>
       <c r="T11" t="n">
-        <v>2779.761337776994</v>
+        <v>2591.957223879615</v>
       </c>
       <c r="U11" t="n">
-        <v>2351.254977626882</v>
+        <v>2163.450863729503</v>
       </c>
       <c r="V11" t="n">
-        <v>1942.314549175544</v>
+        <v>1754.510435278166</v>
       </c>
       <c r="W11" t="n">
-        <v>1942.314549175544</v>
+        <v>1336.961469640845</v>
       </c>
       <c r="X11" t="n">
-        <v>1571.322798205173</v>
+        <v>965.9697186704734</v>
       </c>
       <c r="Y11" t="n">
-        <v>1282.113270242742</v>
+        <v>676.7601907080427</v>
       </c>
     </row>
     <row r="12">
@@ -5120,13 +5120,13 @@
         <v>1325.664675832448</v>
       </c>
       <c r="M12" t="n">
-        <v>1634.495217575307</v>
+        <v>1430.670920121557</v>
       </c>
       <c r="N12" t="n">
-        <v>1990.525502182875</v>
+        <v>1786.701204729125</v>
       </c>
       <c r="O12" t="n">
-        <v>2452.317953866594</v>
+        <v>2248.493656412844</v>
       </c>
       <c r="P12" t="n">
         <v>2583.773000882351</v>
@@ -5205,13 +5205,13 @@
         <v>409.3389893823512</v>
       </c>
       <c r="O13" t="n">
-        <v>65.12</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="P13" t="n">
-        <v>65.12</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.12</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="R13" t="n">
         <v>65.12</v>
@@ -5254,7 +5254,7 @@
         <v>291.9779198897361</v>
       </c>
       <c r="E14" t="n">
-        <v>220.5640694020322</v>
+        <v>137.0655061454243</v>
       </c>
       <c r="F14" t="n">
         <v>65.12</v>
@@ -5348,19 +5348,19 @@
         <v>98.65487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>471.1013981428639</v>
+        <v>387.1477067497204</v>
       </c>
       <c r="K15" t="n">
-        <v>908.7842142372473</v>
+        <v>576.3405228441038</v>
       </c>
       <c r="L15" t="n">
-        <v>1180.134675832447</v>
+        <v>847.690984439304</v>
       </c>
       <c r="M15" t="n">
-        <v>1266.215217575306</v>
+        <v>1182.261526182163</v>
       </c>
       <c r="N15" t="n">
-        <v>1647.985502182875</v>
+        <v>1564.031810789731</v>
       </c>
       <c r="O15" t="n">
         <v>2051.564262473451</v>
@@ -5439,16 +5439,16 @@
         <v>599.0397446017254</v>
       </c>
       <c r="N16" t="n">
-        <v>544.7556226521192</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="O16" t="n">
-        <v>544.7556226521192</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="P16" t="n">
-        <v>544.7556226521192</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="Q16" t="n">
-        <v>65.12</v>
+        <v>119.4041219496062</v>
       </c>
       <c r="R16" t="n">
         <v>65.12</v>
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>880.1035184729978</v>
+        <v>879.6685602764463</v>
       </c>
       <c r="C17" t="n">
-        <v>707.906974793206</v>
+        <v>707.4720165966545</v>
       </c>
       <c r="D17" t="n">
-        <v>575.2411609145698</v>
+        <v>574.8062027180183</v>
       </c>
       <c r="E17" t="n">
-        <v>448.6115754530863</v>
+        <v>448.1766172565348</v>
       </c>
       <c r="F17" t="n">
-        <v>321.4503343338824</v>
+        <v>321.0153761373309</v>
       </c>
       <c r="G17" t="n">
         <v>195.4327865692196</v>
@@ -5506,19 +5506,19 @@
         <v>65.12</v>
       </c>
       <c r="J17" t="n">
-        <v>177.7653900957659</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K17" t="n">
         <v>887.4717564436343</v>
       </c>
       <c r="L17" t="n">
-        <v>1693.331756443634</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="M17" t="n">
-        <v>2204.180585172569</v>
+        <v>1398.320585172569</v>
       </c>
       <c r="N17" t="n">
-        <v>2817.400904947332</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="O17" t="n">
         <v>2817.400904947332</v>
@@ -5533,25 +5533,25 @@
         <v>3256</v>
       </c>
       <c r="S17" t="n">
-        <v>3038.406505870973</v>
+        <v>3037.971547674421</v>
       </c>
       <c r="T17" t="n">
-        <v>2727.623089983534</v>
+        <v>2727.188131786983</v>
       </c>
       <c r="U17" t="n">
-        <v>2353.662184378877</v>
+        <v>2353.227226182325</v>
       </c>
       <c r="V17" t="n">
-        <v>1999.267210472994</v>
+        <v>1998.832252276443</v>
       </c>
       <c r="W17" t="n">
-        <v>1636.263699381128</v>
+        <v>1635.828741184576</v>
       </c>
       <c r="X17" t="n">
-        <v>1319.817402956211</v>
+        <v>1319.382444759659</v>
       </c>
       <c r="Y17" t="n">
-        <v>1085.153329539235</v>
+        <v>1084.718371342683</v>
       </c>
     </row>
     <row r="18">
@@ -5588,10 +5588,10 @@
         <v>250.3313981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>439.5242142372473</v>
+        <v>715.7342142372473</v>
       </c>
       <c r="L18" t="n">
-        <v>864.9885601968795</v>
+        <v>1141.198560196879</v>
       </c>
       <c r="M18" t="n">
         <v>1227.279101939739</v>
@@ -5685,7 +5685,7 @@
         <v>859.3027230120967</v>
       </c>
       <c r="Q19" t="n">
-        <v>517.2433615971223</v>
+        <v>407.9499286428058</v>
       </c>
       <c r="R19" t="n">
         <v>65.12</v>
@@ -5743,25 +5743,25 @@
         <v>65.12</v>
       </c>
       <c r="J20" t="n">
-        <v>65.12</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>774.8263663478684</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L20" t="n">
-        <v>1580.686366347868</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="M20" t="n">
-        <v>2091.535195076804</v>
+        <v>1676.984308114459</v>
       </c>
       <c r="N20" t="n">
-        <v>2704.755514851567</v>
+        <v>2290.204627889222</v>
       </c>
       <c r="O20" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P20" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>3256</v>
@@ -5770,25 +5770,25 @@
         <v>3256</v>
       </c>
       <c r="S20" t="n">
-        <v>3037.971547674421</v>
+        <v>3038.406505870973</v>
       </c>
       <c r="T20" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.623089983534</v>
       </c>
       <c r="U20" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.662184378877</v>
       </c>
       <c r="V20" t="n">
-        <v>1998.832252276443</v>
+        <v>1999.267210472994</v>
       </c>
       <c r="W20" t="n">
-        <v>1635.828741184576</v>
+        <v>1636.263699381128</v>
       </c>
       <c r="X20" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.817402956211</v>
       </c>
       <c r="Y20" t="n">
-        <v>1084.718371342683</v>
+        <v>1085.153329539235</v>
       </c>
     </row>
     <row r="21">
@@ -5822,19 +5822,19 @@
         <v>126.374877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>526.5413981428638</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>869.8480986016793</v>
+        <v>439.5242142372473</v>
       </c>
       <c r="L21" t="n">
-        <v>1141.198560196879</v>
+        <v>710.8746758324473</v>
       </c>
       <c r="M21" t="n">
-        <v>1227.279101939739</v>
+        <v>796.9552175753066</v>
       </c>
       <c r="N21" t="n">
-        <v>1360.559386547307</v>
+        <v>1206.445502182875</v>
       </c>
       <c r="O21" t="n">
         <v>1599.601838231026</v>
@@ -5919,10 +5919,10 @@
         <v>859.3027230120967</v>
       </c>
       <c r="P22" t="n">
-        <v>859.3027230120967</v>
+        <v>446.72908934717</v>
       </c>
       <c r="Q22" t="n">
-        <v>517.2433615971223</v>
+        <v>65.12</v>
       </c>
       <c r="R22" t="n">
         <v>65.12</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>879.6685602765154</v>
+        <v>879.6685602764463</v>
       </c>
       <c r="C23" t="n">
-        <v>707.4720165967236</v>
+        <v>707.4720165966545</v>
       </c>
       <c r="D23" t="n">
-        <v>574.8062027180874</v>
+        <v>575.2411609145698</v>
       </c>
       <c r="E23" t="n">
-        <v>448.1766172566039</v>
+        <v>448.6115754530863</v>
       </c>
       <c r="F23" t="n">
-        <v>321.0153761374</v>
+        <v>321.4503343338824</v>
       </c>
       <c r="G23" t="n">
-        <v>194.9978283727372</v>
+        <v>195.4327865692196</v>
       </c>
       <c r="H23" t="n">
         <v>65.12</v>
@@ -5983,16 +5983,16 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>1166.135479385524</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="L23" t="n">
-        <v>1166.135479385524</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="M23" t="n">
-        <v>1676.984308114459</v>
+        <v>1398.320585172569</v>
       </c>
       <c r="N23" t="n">
-        <v>2290.204627889222</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="O23" t="n">
         <v>2817.400904947332</v>
@@ -6004,28 +6004,28 @@
         <v>3256</v>
       </c>
       <c r="R23" t="n">
-        <v>3256.000000000069</v>
+        <v>3256</v>
       </c>
       <c r="S23" t="n">
-        <v>3037.97154767449</v>
+        <v>3037.971547674421</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.188131787052</v>
+        <v>2727.188131786983</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.227226182395</v>
+        <v>2353.227226182325</v>
       </c>
       <c r="V23" t="n">
-        <v>1998.832252276512</v>
+        <v>1998.832252276443</v>
       </c>
       <c r="W23" t="n">
-        <v>1635.828741184645</v>
+        <v>1635.828741184576</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.382444759729</v>
+        <v>1319.382444759659</v>
       </c>
       <c r="Y23" t="n">
-        <v>1084.718371342752</v>
+        <v>1084.718371342683</v>
       </c>
     </row>
     <row r="24">
@@ -6059,22 +6059,22 @@
         <v>126.374877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>526.5413981428638</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>869.8480986016793</v>
+        <v>439.5242142372473</v>
       </c>
       <c r="L24" t="n">
-        <v>1141.198560196879</v>
+        <v>710.8746758324473</v>
       </c>
       <c r="M24" t="n">
-        <v>1227.279101939739</v>
+        <v>796.9552175753066</v>
       </c>
       <c r="N24" t="n">
-        <v>1360.559386547307</v>
+        <v>1084.349386547307</v>
       </c>
       <c r="O24" t="n">
-        <v>1599.601838231026</v>
+        <v>1323.391838231026</v>
       </c>
       <c r="P24" t="n">
         <v>1712.131182700533</v>
@@ -6156,10 +6156,10 @@
         <v>859.3027230120967</v>
       </c>
       <c r="P25" t="n">
-        <v>859.3027230120967</v>
+        <v>516.472794369291</v>
       </c>
       <c r="Q25" t="n">
-        <v>517.2433615971223</v>
+        <v>65.12</v>
       </c>
       <c r="R25" t="n">
         <v>65.12</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253.1649250963515</v>
+        <v>1022.389550081067</v>
       </c>
       <c r="C26" t="n">
-        <v>61.84</v>
+        <v>795.6475518558203</v>
       </c>
       <c r="D26" t="n">
-        <v>61.84</v>
+        <v>608.4362834317296</v>
       </c>
       <c r="E26" t="n">
-        <v>61.84</v>
+        <v>427.2612434247916</v>
       </c>
       <c r="F26" t="n">
-        <v>61.84</v>
+        <v>427.2612434247916</v>
       </c>
       <c r="G26" t="n">
-        <v>61.84</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="H26" t="n">
         <v>61.84</v>
@@ -6220,16 +6220,16 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K26" t="n">
-        <v>453.1491130376558</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>1218.419113037656</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>1729.267941766591</v>
+        <v>1673.704308114459</v>
       </c>
       <c r="N26" t="n">
-        <v>2342.488261541354</v>
+        <v>2286.924627889222</v>
       </c>
       <c r="O26" t="n">
         <v>2653.400904947332</v>
@@ -6244,25 +6244,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>2793.286094312508</v>
+        <v>3065.860001183541</v>
       </c>
       <c r="T26" t="n">
-        <v>2427.957223879615</v>
+        <v>2788.241420412993</v>
       </c>
       <c r="U26" t="n">
-        <v>1999.450863729503</v>
+        <v>2359.735060262881</v>
       </c>
       <c r="V26" t="n">
-        <v>1590.510435278166</v>
+        <v>2359.735060262881</v>
       </c>
       <c r="W26" t="n">
-        <v>1172.961469640845</v>
+        <v>1942.18609462556</v>
       </c>
       <c r="X26" t="n">
-        <v>801.9697186704736</v>
+        <v>1571.194343655189</v>
       </c>
       <c r="Y26" t="n">
-        <v>512.760190708043</v>
+        <v>1281.984815692758</v>
       </c>
     </row>
     <row r="27">
@@ -6299,19 +6299,19 @@
         <v>416.3413981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>624.4599167834981</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1118.560378378698</v>
+        <v>1322.384675832448</v>
       </c>
       <c r="M27" t="n">
-        <v>1427.390920121557</v>
+        <v>1631.215217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1783.421204729126</v>
+        <v>1987.245502182875</v>
       </c>
       <c r="O27" t="n">
-        <v>2245.213656412845</v>
+        <v>2449.037953866594</v>
       </c>
       <c r="P27" t="n">
         <v>2580.493000882351</v>
@@ -6351,19 +6351,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>209.3150479114819</v>
+        <v>282.6094938783241</v>
       </c>
       <c r="C28" t="n">
-        <v>183.3432818122532</v>
+        <v>234.4021740318143</v>
       </c>
       <c r="D28" t="n">
-        <v>122.1955868066416</v>
+        <v>173.2544790262027</v>
       </c>
       <c r="E28" t="n">
-        <v>65.64921828446326</v>
+        <v>116.7081105040244</v>
       </c>
       <c r="F28" t="n">
-        <v>65.64921828446326</v>
+        <v>66.82643780933554</v>
       </c>
       <c r="G28" t="n">
         <v>65.64921828446326</v>
@@ -6378,49 +6378,49 @@
         <v>297.5566195885342</v>
       </c>
       <c r="K28" t="n">
-        <v>297.5566195885342</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="L28" t="n">
-        <v>97.0034598332017</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="M28" t="n">
-        <v>97.0034598332017</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="N28" t="n">
-        <v>97.0034598332017</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="O28" t="n">
-        <v>97.0034598332017</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="P28" t="n">
-        <v>97.0034598332017</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="Q28" t="n">
-        <v>97.0034598332017</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="R28" t="n">
-        <v>97.0034598332017</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="S28" t="n">
-        <v>97.0034598332017</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="T28" t="n">
-        <v>111.8291389920066</v>
+        <v>248.2199009684067</v>
       </c>
       <c r="U28" t="n">
-        <v>185.1303316302932</v>
+        <v>321.5210936066933</v>
       </c>
       <c r="V28" t="n">
-        <v>210.7017245162392</v>
+        <v>347.0924864926393</v>
       </c>
       <c r="W28" t="n">
-        <v>209.3150479114819</v>
+        <v>345.705809887882</v>
       </c>
       <c r="X28" t="n">
-        <v>209.3150479114819</v>
+        <v>345.705809887882</v>
       </c>
       <c r="Y28" t="n">
-        <v>209.3150479114819</v>
+        <v>282.6094938783241</v>
       </c>
     </row>
     <row r="29">
@@ -6433,10 +6433,10 @@
         <v>253.1649250963515</v>
       </c>
       <c r="C29" t="n">
-        <v>61.84</v>
+        <v>243.0150400069381</v>
       </c>
       <c r="D29" t="n">
-        <v>61.84</v>
+        <v>243.0150400069381</v>
       </c>
       <c r="E29" t="n">
         <v>61.84</v>
@@ -6466,10 +6466,10 @@
         <v>1673.704308114459</v>
       </c>
       <c r="N29" t="n">
-        <v>2286.924627889222</v>
+        <v>1888.130904947299</v>
       </c>
       <c r="O29" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947299</v>
       </c>
       <c r="P29" t="n">
         <v>2653.400904947332</v>
@@ -6542,7 +6542,7 @@
         <v>1322.384675832448</v>
       </c>
       <c r="M30" t="n">
-        <v>1427.390920121557</v>
+        <v>1631.215217575307</v>
       </c>
       <c r="N30" t="n">
         <v>1783.421204729126</v>
@@ -6630,7 +6630,7 @@
         <v>406.0589893823512</v>
       </c>
       <c r="P31" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="Q31" t="n">
         <v>61.84</v>
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>804.0962457457251</v>
+        <v>812.6382572461436</v>
       </c>
       <c r="C32" t="n">
-        <v>644.0209141871454</v>
+        <v>652.5629256875638</v>
       </c>
       <c r="D32" t="n">
-        <v>523.4763124297214</v>
+        <v>532.0183239301398</v>
       </c>
       <c r="E32" t="n">
-        <v>408.96793908945</v>
+        <v>417.5099505898684</v>
       </c>
       <c r="F32" t="n">
-        <v>293.9279100914582</v>
+        <v>302.4699215918766</v>
       </c>
       <c r="G32" t="n">
-        <v>180.0315744480075</v>
+        <v>188.5735859484259</v>
       </c>
       <c r="H32" t="n">
-        <v>61.84</v>
+        <v>70.38201150041843</v>
       </c>
       <c r="I32" t="n">
         <v>61.84</v>
       </c>
       <c r="J32" t="n">
-        <v>61.84</v>
+        <v>445.5561922637026</v>
       </c>
       <c r="K32" t="n">
-        <v>76.4556038871856</v>
+        <v>1155.056868702876</v>
       </c>
       <c r="L32" t="n">
-        <v>61.84</v>
+        <v>1139.518787894795</v>
       </c>
       <c r="M32" t="n">
-        <v>567.5230483919338</v>
+        <v>1645.201836286729</v>
       </c>
       <c r="N32" t="n">
-        <v>1177.656143764612</v>
+        <v>2255.334931659408</v>
       </c>
       <c r="O32" t="n">
-        <v>1942.926143764654</v>
+        <v>2675.571728341327</v>
       </c>
       <c r="P32" t="n">
-        <v>2708.196143764696</v>
+        <v>2660.033647533245</v>
       </c>
       <c r="Q32" t="n">
         <v>3092</v>
       </c>
       <c r="R32" t="n">
-        <v>3083.457988499581</v>
+        <v>3092</v>
       </c>
       <c r="S32" t="n">
-        <v>2877.550748295214</v>
+        <v>2886.092759795633</v>
       </c>
       <c r="T32" t="n">
-        <v>2578.888544528988</v>
+        <v>2587.430556029407</v>
       </c>
       <c r="U32" t="n">
-        <v>2217.048851045543</v>
+        <v>2225.590862545962</v>
       </c>
       <c r="V32" t="n">
-        <v>1874.775089260873</v>
+        <v>1883.317100761291</v>
       </c>
       <c r="W32" t="n">
-        <v>1523.892790290219</v>
+        <v>1532.434801790637</v>
       </c>
       <c r="X32" t="n">
-        <v>1219.567705986514</v>
+        <v>1228.109717486932</v>
       </c>
       <c r="Y32" t="n">
-        <v>997.0248446907499</v>
+        <v>1005.566856191168</v>
       </c>
     </row>
     <row r="33">
@@ -6770,25 +6770,25 @@
         <v>134.974877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>258.9313981428639</v>
+        <v>483.6771006891146</v>
       </c>
       <c r="K33" t="n">
-        <v>736.2142142372473</v>
+        <v>672.869916783498</v>
       </c>
       <c r="L33" t="n">
-        <v>1007.564675832447</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M33" t="n">
-        <v>1093.645217575307</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N33" t="n">
-        <v>1226.925502182875</v>
+        <v>1163.581204729126</v>
       </c>
       <c r="O33" t="n">
-        <v>1465.967953866594</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P33" t="n">
-        <v>1578.4972983361</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q33" t="n">
         <v>1631.894528442776</v>
@@ -6825,52 +6825,52 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>486.0066123122328</v>
+        <v>486.0066123122566</v>
       </c>
       <c r="C34" t="n">
-        <v>504.0986181306686</v>
+        <v>504.0986181306923</v>
       </c>
       <c r="D34" t="n">
-        <v>509.5077622556687</v>
+        <v>509.5077622556924</v>
       </c>
       <c r="E34" t="n">
-        <v>519.4266664670818</v>
+        <v>519.4266664671054</v>
       </c>
       <c r="F34" t="n">
-        <v>535.8776390590173</v>
+        <v>535.8776390590409</v>
       </c>
       <c r="G34" t="n">
-        <v>581.3742049459025</v>
+        <v>581.3742049459262</v>
       </c>
       <c r="H34" t="n">
-        <v>642.9807901053001</v>
+        <v>642.9807901053238</v>
       </c>
       <c r="I34" t="n">
-        <v>756.203669041383</v>
+        <v>756.2036690414067</v>
       </c>
       <c r="J34" t="n">
-        <v>1009.377409693834</v>
+        <v>1009.377409693858</v>
       </c>
       <c r="K34" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="L34" t="n">
-        <v>1011.831843630703</v>
+        <v>877.9453505420606</v>
       </c>
       <c r="M34" t="n">
-        <v>1011.831843630703</v>
+        <v>645.9942279132224</v>
       </c>
       <c r="N34" t="n">
-        <v>1011.831843630703</v>
+        <v>645.9942279132224</v>
       </c>
       <c r="O34" t="n">
-        <v>902.2945710196249</v>
+        <v>462.2924215437147</v>
       </c>
       <c r="P34" t="n">
-        <v>501.8421494759102</v>
+        <v>61.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>501.8421494759102</v>
+        <v>61.84</v>
       </c>
       <c r="R34" t="n">
         <v>61.84</v>
@@ -6931,19 +6931,19 @@
         <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>430.0181114556215</v>
+        <v>810.0236653847963</v>
       </c>
       <c r="L35" t="n">
-        <v>415.4025075684376</v>
+        <v>1575.293665384796</v>
       </c>
       <c r="M35" t="n">
-        <v>519.3605521604688</v>
+        <v>2080.97671377673</v>
       </c>
       <c r="N35" t="n">
-        <v>1129.493647533147</v>
+        <v>2691.109809149409</v>
       </c>
       <c r="O35" t="n">
-        <v>1894.763647533196</v>
+        <v>2675.571728341327</v>
       </c>
       <c r="P35" t="n">
         <v>2660.033647533245</v>
@@ -6952,25 +6952,25 @@
         <v>3092</v>
       </c>
       <c r="R35" t="n">
-        <v>3092</v>
+        <v>3083.457988499581</v>
       </c>
       <c r="S35" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T35" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U35" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V35" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W35" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X35" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y35" t="n">
         <v>997.0248446907499</v>
@@ -7007,19 +7007,19 @@
         <v>134.974877967565</v>
       </c>
       <c r="J36" t="n">
-        <v>483.6771006891146</v>
+        <v>258.9313981428639</v>
       </c>
       <c r="K36" t="n">
-        <v>672.869916783498</v>
+        <v>448.1242142372473</v>
       </c>
       <c r="L36" t="n">
-        <v>944.220378378698</v>
+        <v>719.4746758324475</v>
       </c>
       <c r="M36" t="n">
-        <v>1030.300920121557</v>
+        <v>805.5552175753068</v>
       </c>
       <c r="N36" t="n">
-        <v>1163.581204729126</v>
+        <v>938.8355021828751</v>
       </c>
       <c r="O36" t="n">
         <v>1402.623656412844</v>
@@ -7141,43 +7141,43 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>804.0962457457251</v>
+        <v>812.6382572461436</v>
       </c>
       <c r="C38" t="n">
-        <v>644.0209141871454</v>
+        <v>652.5629256875638</v>
       </c>
       <c r="D38" t="n">
-        <v>523.4763124297214</v>
+        <v>532.0183239301398</v>
       </c>
       <c r="E38" t="n">
-        <v>408.96793908945</v>
+        <v>417.5099505898684</v>
       </c>
       <c r="F38" t="n">
-        <v>293.9279100914582</v>
+        <v>302.4699215918766</v>
       </c>
       <c r="G38" t="n">
-        <v>180.0315744480075</v>
+        <v>188.5735859484259</v>
       </c>
       <c r="H38" t="n">
-        <v>61.84</v>
+        <v>70.38201150041843</v>
       </c>
       <c r="I38" t="n">
         <v>61.84</v>
       </c>
       <c r="J38" t="n">
-        <v>445.5561922637023</v>
+        <v>61.84</v>
       </c>
       <c r="K38" t="n">
-        <v>810.0236653847411</v>
+        <v>771.340676439175</v>
       </c>
       <c r="L38" t="n">
-        <v>794.4855845766601</v>
+        <v>1536.610676439175</v>
       </c>
       <c r="M38" t="n">
-        <v>1300.168632968594</v>
+        <v>2042.293724831108</v>
       </c>
       <c r="N38" t="n">
-        <v>1910.301728341272</v>
+        <v>2652.426820203787</v>
       </c>
       <c r="O38" t="n">
         <v>2675.571728341328</v>
@@ -7189,28 +7189,28 @@
         <v>3092</v>
       </c>
       <c r="R38" t="n">
-        <v>3083.457988499581</v>
+        <v>3092</v>
       </c>
       <c r="S38" t="n">
-        <v>2877.550748295214</v>
+        <v>2886.092759795633</v>
       </c>
       <c r="T38" t="n">
-        <v>2578.888544528988</v>
+        <v>2587.430556029407</v>
       </c>
       <c r="U38" t="n">
-        <v>2217.048851045543</v>
+        <v>2225.590862545962</v>
       </c>
       <c r="V38" t="n">
-        <v>1874.775089260873</v>
+        <v>1883.317100761291</v>
       </c>
       <c r="W38" t="n">
-        <v>1523.892790290219</v>
+        <v>1532.434801790637</v>
       </c>
       <c r="X38" t="n">
-        <v>1219.567705986514</v>
+        <v>1228.109717486932</v>
       </c>
       <c r="Y38" t="n">
-        <v>997.0248446907499</v>
+        <v>1005.566856191168</v>
       </c>
     </row>
     <row r="39">
@@ -7250,10 +7250,10 @@
         <v>448.1242142372473</v>
       </c>
       <c r="L39" t="n">
-        <v>719.4746758324475</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M39" t="n">
-        <v>805.5552175753068</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N39" t="n">
         <v>1163.581204729126</v>
@@ -7299,55 +7299,55 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>486.0066123122328</v>
+        <v>486.0066123122601</v>
       </c>
       <c r="C40" t="n">
-        <v>504.0986181306686</v>
+        <v>504.0986181306959</v>
       </c>
       <c r="D40" t="n">
-        <v>509.5077622556687</v>
+        <v>509.507762255696</v>
       </c>
       <c r="E40" t="n">
-        <v>519.4266664670818</v>
+        <v>519.426666467109</v>
       </c>
       <c r="F40" t="n">
-        <v>535.8776390590173</v>
+        <v>535.8776390590446</v>
       </c>
       <c r="G40" t="n">
-        <v>581.3742049459025</v>
+        <v>581.3742049459298</v>
       </c>
       <c r="H40" t="n">
-        <v>642.9807901053001</v>
+        <v>642.9807901053274</v>
       </c>
       <c r="I40" t="n">
-        <v>756.203669041383</v>
+        <v>756.2036690414103</v>
       </c>
       <c r="J40" t="n">
-        <v>1009.377409693834</v>
+        <v>1009.377409693862</v>
       </c>
       <c r="K40" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.83184363073</v>
       </c>
       <c r="L40" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.83184363073</v>
       </c>
       <c r="M40" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.83184363073</v>
       </c>
       <c r="N40" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.83184363073</v>
       </c>
       <c r="O40" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.83184363073</v>
       </c>
       <c r="P40" t="n">
-        <v>1011.831843630703</v>
+        <v>941.0737317239891</v>
       </c>
       <c r="Q40" t="n">
-        <v>572.600261382624</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="R40" t="n">
-        <v>132.5981119067138</v>
+        <v>61.84</v>
       </c>
       <c r="S40" t="n">
         <v>61.84</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>806.2192175517926</v>
+        <v>880.5115846918088</v>
       </c>
       <c r="C41" t="n">
-        <v>567.356007205334</v>
+        <v>641.6483743453502</v>
       </c>
       <c r="D41" t="n">
-        <v>567.356007205334</v>
+        <v>641.6483743453502</v>
       </c>
       <c r="E41" t="n">
-        <v>374.0597550771838</v>
+        <v>448.3521222172001</v>
       </c>
       <c r="F41" t="n">
-        <v>374.0597550771838</v>
+        <v>254.5242144313295</v>
       </c>
       <c r="G41" t="n">
-        <v>258.8194532358863</v>
+        <v>61.84</v>
       </c>
       <c r="H41" t="n">
         <v>61.84</v>
@@ -7429,25 +7429,25 @@
         <v>3053.738789062329</v>
       </c>
       <c r="S41" t="n">
-        <v>3053.738789062329</v>
+        <v>2769.043670070084</v>
       </c>
       <c r="T41" t="n">
-        <v>3053.738789062329</v>
+        <v>2769.043670070084</v>
       </c>
       <c r="U41" t="n">
-        <v>2613.111216791005</v>
+        <v>2328.41609779876</v>
       </c>
       <c r="V41" t="n">
-        <v>2192.049576218456</v>
+        <v>1994.625465625568</v>
       </c>
       <c r="W41" t="n">
-        <v>1762.379398459923</v>
+        <v>1564.955287867035</v>
       </c>
       <c r="X41" t="n">
-        <v>1379.266435368339</v>
+        <v>1181.842324775452</v>
       </c>
       <c r="Y41" t="n">
-        <v>1077.935695284696</v>
+        <v>880.5115846918088</v>
       </c>
     </row>
     <row r="42">
@@ -7481,10 +7481,10 @@
         <v>61.84</v>
       </c>
       <c r="J42" t="n">
-        <v>342.8083563952046</v>
+        <v>342.8083563952047</v>
       </c>
       <c r="K42" t="n">
-        <v>742.8711724895879</v>
+        <v>742.8711724895882</v>
       </c>
       <c r="L42" t="n">
         <v>1225.091634084788</v>
@@ -7493,7 +7493,7 @@
         <v>1522.042175827647</v>
       </c>
       <c r="N42" t="n">
-        <v>1866.192460435215</v>
+        <v>1866.192460435216</v>
       </c>
       <c r="O42" t="n">
         <v>2316.104912118934</v>
@@ -7508,16 +7508,16 @@
         <v>2341.375483853533</v>
       </c>
       <c r="S42" t="n">
-        <v>2085.250231364027</v>
+        <v>2224.105224033037</v>
       </c>
       <c r="T42" t="n">
-        <v>1890.949458417043</v>
+        <v>2029.804451086053</v>
       </c>
       <c r="U42" t="n">
-        <v>1701.848084921905</v>
+        <v>1840.703077590915</v>
       </c>
       <c r="V42" t="n">
-        <v>1498.301956445622</v>
+        <v>1637.156949114632</v>
       </c>
       <c r="W42" t="n">
         <v>1415.567915872381</v>
@@ -7560,40 +7560,40 @@
         <v>61.84</v>
       </c>
       <c r="J43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="K43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="L43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="M43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="N43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="O43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="P43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="Q43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="R43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="S43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="T43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="U43" t="n">
-        <v>91.27831913164476</v>
+        <v>77.58692624569879</v>
       </c>
       <c r="V43" t="n">
         <v>91.27831913164476</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>639.0164548048064</v>
+        <v>946.0313599411581</v>
       </c>
       <c r="C44" t="n">
-        <v>373.8906181957216</v>
+        <v>946.0313599411581</v>
       </c>
       <c r="D44" t="n">
-        <v>148.2955113877925</v>
+        <v>720.436253133229</v>
       </c>
       <c r="E44" t="n">
-        <v>148.2955113877925</v>
+        <v>500.8773747424526</v>
       </c>
       <c r="F44" t="n">
-        <v>148.2955113877925</v>
+        <v>280.7868406939558</v>
       </c>
       <c r="G44" t="n">
-        <v>148.2955113877925</v>
+        <v>61.84</v>
       </c>
       <c r="H44" t="n">
         <v>61.84</v>
@@ -7639,19 +7639,19 @@
         <v>61.84</v>
       </c>
       <c r="J44" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="K44" t="n">
-        <v>1162.855479385524</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="L44" t="n">
-        <v>1162.855479385524</v>
+        <v>1529.331756443634</v>
       </c>
       <c r="M44" t="n">
-        <v>1673.704308114459</v>
+        <v>2040.180585172569</v>
       </c>
       <c r="N44" t="n">
-        <v>2286.924627889222</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="O44" t="n">
         <v>2653.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>3092</v>
       </c>
       <c r="R44" t="n">
-        <v>3027.476162799703</v>
+        <v>3092</v>
       </c>
       <c r="S44" t="n">
-        <v>2716.518417544831</v>
+        <v>2781.042254745129</v>
       </c>
       <c r="T44" t="n">
-        <v>2716.518417544831</v>
+        <v>2436.912223658326</v>
       </c>
       <c r="U44" t="n">
-        <v>2249.628219010881</v>
+        <v>2436.912223658326</v>
       </c>
       <c r="V44" t="n">
-        <v>1802.303952175705</v>
+        <v>2436.912223658326</v>
       </c>
       <c r="W44" t="n">
-        <v>1346.371148154546</v>
+        <v>1980.979419637167</v>
       </c>
       <c r="X44" t="n">
-        <v>936.9955588003362</v>
+        <v>1571.603830282957</v>
       </c>
       <c r="Y44" t="n">
-        <v>936.9955588003362</v>
+        <v>1244.010463936688</v>
       </c>
     </row>
     <row r="45">
@@ -7724,37 +7724,37 @@
         <v>745.2493362696823</v>
       </c>
       <c r="L45" t="n">
-        <v>1086.249287752187</v>
+        <v>1201.729797864882</v>
       </c>
       <c r="M45" t="n">
-        <v>1357.459829495047</v>
+        <v>1373.148353424001</v>
       </c>
       <c r="N45" t="n">
-        <v>1675.870114102615</v>
+        <v>1691.55863803157</v>
       </c>
       <c r="O45" t="n">
-        <v>2100.042565786334</v>
+        <v>2115.731089715289</v>
       </c>
       <c r="P45" t="n">
-        <v>2397.701910255841</v>
+        <v>2413.390434184796</v>
       </c>
       <c r="Q45" t="n">
-        <v>2397.701910255841</v>
+        <v>2427.171961745221</v>
       </c>
       <c r="R45" t="n">
-        <v>2343.930332204927</v>
+        <v>2427.171961745221</v>
       </c>
       <c r="S45" t="n">
-        <v>2343.930332204927</v>
+        <v>2427.171961745221</v>
       </c>
       <c r="T45" t="n">
-        <v>2123.366932995317</v>
+        <v>2206.608562535611</v>
       </c>
       <c r="U45" t="n">
-        <v>1908.002933237553</v>
+        <v>1991.244562777847</v>
       </c>
       <c r="V45" t="n">
-        <v>1678.194178498644</v>
+        <v>1761.435808038937</v>
       </c>
       <c r="W45" t="n">
         <v>1678.194178498644</v>
@@ -7797,43 +7797,43 @@
         <v>61.84</v>
       </c>
       <c r="J46" t="n">
-        <v>113.9037576312383</v>
+        <v>61.84</v>
       </c>
       <c r="K46" t="n">
-        <v>113.9037576312383</v>
+        <v>61.84</v>
       </c>
       <c r="L46" t="n">
-        <v>113.9037576312383</v>
+        <v>61.84</v>
       </c>
       <c r="M46" t="n">
-        <v>113.9037576312383</v>
+        <v>61.84</v>
       </c>
       <c r="N46" t="n">
-        <v>113.9037576312383</v>
+        <v>61.84</v>
       </c>
       <c r="O46" t="n">
-        <v>113.9037576312383</v>
+        <v>61.84</v>
       </c>
       <c r="P46" t="n">
-        <v>113.9037576312383</v>
+        <v>61.84</v>
       </c>
       <c r="Q46" t="n">
-        <v>113.9037576312383</v>
+        <v>61.84</v>
       </c>
       <c r="R46" t="n">
-        <v>113.9037576312383</v>
+        <v>61.84</v>
       </c>
       <c r="S46" t="n">
-        <v>113.9037576312383</v>
+        <v>61.84</v>
       </c>
       <c r="T46" t="n">
-        <v>113.9037576312383</v>
+        <v>61.84</v>
       </c>
       <c r="U46" t="n">
-        <v>113.9037576312383</v>
+        <v>61.84</v>
       </c>
       <c r="V46" t="n">
-        <v>101.6105149885956</v>
+        <v>61.84</v>
       </c>
       <c r="W46" t="n">
         <v>61.84</v>
@@ -7967,7 +7967,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>500.8454983898772</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
-        <v>1096.663422488788</v>
+        <v>880.6338033555658</v>
       </c>
       <c r="O2" t="n">
         <v>884.2478695740924</v>
@@ -8201,10 +8201,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>214.2751174529344</v>
+        <v>117.1502349760341</v>
       </c>
       <c r="K5" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8219,7 +8219,7 @@
         <v>884.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2870600406814674</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q5" t="n">
         <v>615.8520732695737</v>
@@ -8441,22 +8441,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>202.8544162978973</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>544.2621276423127</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>884.2478695740924</v>
+        <v>668.2182504408663</v>
       </c>
       <c r="P8" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406860149</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -9149,13 +9149,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>148.8262285640457</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="L17" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,7 +9164,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
@@ -9386,13 +9386,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>814.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,13 +9401,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>627.0604808351362</v>
+        <v>602.7693615519817</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,7 +9626,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -9638,7 +9638,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>602.7693615519817</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P23" t="n">
         <v>0.2870600406814136</v>
@@ -9863,10 +9863,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>772.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,7 +9875,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>384.3010447316466</v>
+        <v>440.4259272085471</v>
       </c>
       <c r="P26" t="n">
         <v>0.2870600406814136</v>
@@ -10109,13 +10109,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>1096.663422488788</v>
+        <v>693.8414801232085</v>
       </c>
       <c r="O29" t="n">
-        <v>440.4259272085471</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407153</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10334,10 +10334,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>50.42570624509119</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>29.85214784831386</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10349,13 +10349,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>843.2478695741345</v>
+        <v>501.6649982891932</v>
       </c>
       <c r="P32" t="n">
-        <v>773.2870600407235</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>568.1712020004379</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,22 +10574,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>375.2922462381946</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M35" t="n">
-        <v>662.5632917884291</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>843.2478695741418</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>773.2870600407308</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10808,13 +10808,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>50.42570624509142</v>
       </c>
       <c r="K38" t="n">
-        <v>375.2922462381401</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>772.9999999999998</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
@@ -10823,7 +10823,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>843.247869574149</v>
+        <v>108.5440286302594</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11282,13 +11282,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>765.4397879755212</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11297,7 +11297,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>440.4259272085471</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
@@ -22703,7 +22703,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>5.662449696453123</v>
+        <v>5.6624496964466</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22952,10 +22952,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>29.21007785423586</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>29.21007785422825</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>5.662449696441641</v>
+        <v>5.662449696452228</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23229,16 +23229,16 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>61.28925813745595</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
         <v>183.0096587035274</v>
@@ -23271,10 +23271,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>160.0474739301105</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23286,7 +23286,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>413.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -23420,7 +23420,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O13" t="n">
-        <v>74.66876459048729</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
         <v>462.4478973282775</v>
@@ -23429,7 +23429,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23469,10 +23469,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>82.66357762404181</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>82.66357762404179</v>
       </c>
       <c r="G14" t="n">
         <v>152.7573722870162</v>
@@ -23654,7 +23654,7 @@
         <v>269.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>266.4437945415748</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O16" t="n">
         <v>389.445564079015</v>
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>421.8608472510409</v>
       </c>
       <c r="S16" t="n">
         <v>111.3734797028554</v>
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.4306086145860206</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.430608614585708</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23900,10 +23900,10 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
         <v>108.2004986247733</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -23934,7 +23934,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4306086145800521</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24134,13 +24134,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>108.2004986247733</v>
+        <v>69.04626797189974</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24177,7 +24177,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.4306086145859638</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4306086145176096</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24371,13 +24371,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>69.04626797189979</v>
       </c>
       <c r="Q25" t="n">
-        <v>108.2004986247733</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>35.06290239760591</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,16 +24459,16 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>86.83318676572151</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -24569,7 +24569,7 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>22.01319820980827</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -24578,10 +24578,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>20.04387284153003</v>
+        <v>18.87842551190647</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -24593,10 +24593,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
         <v>295.6316114025499</v>
@@ -24635,7 +24635,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -24648,13 +24648,13 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>35.06290239760591</v>
+        <v>214.4261920044746</v>
       </c>
       <c r="D29" t="n">
         <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>179.8896287080119</v>
@@ -24845,10 +24845,10 @@
         <v>415.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>462.4478973282775</v>
+        <v>121.6710978397498</v>
       </c>
       <c r="Q31" t="n">
-        <v>160.0624669370703</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
         <v>501.6021279811511</v>
@@ -25070,16 +25070,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>241.0036641940478</v>
+        <v>167.5807757732023</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -25088,7 +25088,7 @@
         <v>434.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>71.37347970285543</v>
@@ -25556,7 +25556,7 @@
         <v>349.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>396.4478973282775</v>
+        <v>326.3973665406039</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.322948915208755</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -25605,13 +25605,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>191.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>76.66947346413166</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>195.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,7 +25644,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>281.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>373.6755817285639</v>
@@ -25653,7 +25653,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>86.39829831536417</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -25723,7 +25723,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>137.4664427423198</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>137.4664427423195</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25833,22 +25833,22 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>262.4745782429939</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>217.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>217.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>216.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>135.4187024296128</v>
+        <v>221.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25878,19 +25878,19 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>399.6755817285639</v>
+        <v>58.98685095262914</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>462.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>442.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -25899,7 +25899,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>324.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -25957,7 +25957,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>307.0399350219751</v>
+        <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
         <v>279.5639999646113</v>
@@ -25972,7 +25972,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>245.3731429098285</v>
+        <v>162.9639296649378</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26048,10 +26048,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>39.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>60.44364543010755</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>996036.0883504066</v>
+        <v>996036.0883504067</v>
       </c>
     </row>
     <row r="3">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2632314.886353728</v>
+        <v>2632314.886353729</v>
       </c>
     </row>
     <row r="5">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4124178.072532697</v>
+        <v>4124178.072532698</v>
       </c>
     </row>
     <row r="7">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6501532.258063969</v>
+        <v>6501532.258063965</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7220695.738596853</v>
+        <v>7220695.73859685</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7944382.107210544</v>
+        <v>7944382.10721054</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8743005.844634622</v>
+        <v>8743005.844634619</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9539923.461538402</v>
+        <v>9539923.461538399</v>
       </c>
     </row>
     <row r="14">
@@ -26269,10 +26269,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1384543.598310502</v>
+        <v>1384543.598310503</v>
       </c>
       <c r="C2" t="n">
-        <v>1384543.598310502</v>
+        <v>1384543.598310503</v>
       </c>
       <c r="D2" t="n">
         <v>1384543.598310503</v>
@@ -26290,7 +26290,7 @@
         <v>1341071.591838157</v>
       </c>
       <c r="I2" t="n">
-        <v>1341071.591838162</v>
+        <v>1341071.591838157</v>
       </c>
       <c r="J2" t="n">
         <v>1224700.008423176</v>
@@ -26299,13 +26299,13 @@
         <v>1224700.008423176</v>
       </c>
       <c r="L2" t="n">
-        <v>1348629.813221775</v>
+        <v>1348629.813221776</v>
       </c>
       <c r="M2" t="n">
         <v>1348629.813221775</v>
       </c>
       <c r="N2" t="n">
-        <v>1348629.813221775</v>
+        <v>1348629.813221776</v>
       </c>
       <c r="O2" t="n">
         <v>1188145.666027177</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>614247.5715792079</v>
+        <v>619095.9472656922</v>
       </c>
       <c r="C4" t="n">
-        <v>612495.6628399484</v>
+        <v>617344.0385264327</v>
       </c>
       <c r="D4" t="n">
-        <v>610741.3775271378</v>
+        <v>615589.7532136219</v>
       </c>
       <c r="E4" t="n">
-        <v>532123.603825271</v>
+        <v>536922.2846154374</v>
       </c>
       <c r="F4" t="n">
-        <v>556398.2196192667</v>
+        <v>561196.9004094331</v>
       </c>
       <c r="G4" t="n">
-        <v>581187.6277435899</v>
+        <v>585986.3085337563</v>
       </c>
       <c r="H4" t="n">
-        <v>579514.692803493</v>
+        <v>584313.3735936591</v>
       </c>
       <c r="I4" t="n">
-        <v>577839.4224190691</v>
+        <v>582638.1032092323</v>
       </c>
       <c r="J4" t="n">
-        <v>520323.0592843113</v>
+        <v>524998.4738086244</v>
       </c>
       <c r="K4" t="n">
-        <v>518858.3176303694</v>
+        <v>523533.7321546826</v>
       </c>
       <c r="L4" t="n">
-        <v>581043.8351797319</v>
+        <v>585765.748114326</v>
       </c>
       <c r="M4" t="n">
-        <v>579313.7164781794</v>
+        <v>584035.6294127728</v>
       </c>
       <c r="N4" t="n">
-        <v>577581.1101536271</v>
+        <v>582303.0230882212</v>
       </c>
       <c r="O4" t="n">
-        <v>494869.5309141541</v>
+        <v>499544.9454384673</v>
       </c>
       <c r="P4" t="n">
-        <v>454063.7935190182</v>
+        <v>458739.2080433314</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>400649.2267312941</v>
+        <v>395800.8510448106</v>
       </c>
       <c r="C6" t="n">
-        <v>688929.1354705535</v>
+        <v>684080.7597840703</v>
       </c>
       <c r="D6" t="n">
-        <v>690683.4207833649</v>
+        <v>685835.0450968808</v>
       </c>
       <c r="E6" t="n">
-        <v>458101.5963659051</v>
+        <v>453302.9155757388</v>
       </c>
       <c r="F6" t="n">
-        <v>641354.646106101</v>
+        <v>636555.9653159346</v>
       </c>
       <c r="G6" t="n">
-        <v>664537.5130945662</v>
+        <v>659738.8323043998</v>
       </c>
       <c r="H6" t="n">
-        <v>688610.448034664</v>
+        <v>683811.7672444974</v>
       </c>
       <c r="I6" t="n">
-        <v>690285.7184190933</v>
+        <v>685487.0376289242</v>
       </c>
       <c r="J6" t="n">
-        <v>229567.0241388644</v>
+        <v>224891.6096145515</v>
       </c>
       <c r="K6" t="n">
-        <v>619127.7657928066</v>
+        <v>614452.3512684936</v>
       </c>
       <c r="L6" t="n">
-        <v>620923.499042043</v>
+        <v>616201.5861074498</v>
       </c>
       <c r="M6" t="n">
-        <v>697853.617743596</v>
+        <v>693131.7048090021</v>
       </c>
       <c r="N6" t="n">
-        <v>699586.2240681481</v>
+        <v>694864.3111335544</v>
       </c>
       <c r="O6" t="n">
-        <v>553971.038113023</v>
+        <v>549295.6235887095</v>
       </c>
       <c r="P6" t="n">
-        <v>591442.7871997246</v>
+        <v>586767.3726754116</v>
       </c>
     </row>
   </sheetData>
@@ -27005,10 +27005,10 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>93</v>
@@ -27436,7 +27436,7 @@
         <v>400</v>
       </c>
       <c r="C2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>400</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,13 +27481,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
+        <v>157.3092074428799</v>
+      </c>
+      <c r="T2" t="n">
         <v>400</v>
-      </c>
-      <c r="T2" t="n">
-        <v>56.5117682972699</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27502,7 +27502,7 @@
         <v>400</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
@@ -27515,7 +27515,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27560,13 +27560,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>303.3742880620964</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>342.2743756165773</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27575,7 +27575,7 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -27597,7 +27597,7 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27615,7 +27615,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>243.9079545990498</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
         <v>288.520773801143</v>
@@ -27642,7 +27642,7 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
         <v>400</v>
@@ -27651,7 +27651,7 @@
         <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>330.9720543320648</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
@@ -27670,16 +27670,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>400</v>
-      </c>
-      <c r="E5" t="n">
-        <v>56.51176829727029</v>
       </c>
       <c r="F5" t="n">
         <v>400</v>
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>307.3903671255649</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27718,16 +27718,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V5" t="n">
         <v>400</v>
@@ -27739,7 +27739,7 @@
         <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -27755,7 +27755,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27803,7 +27803,7 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>250.7033677259335</v>
+        <v>302.7656808282309</v>
       </c>
     </row>
     <row r="7">
@@ -27834,22 +27834,22 @@
         <v>400</v>
       </c>
       <c r="D7" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E7" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F7" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G7" t="n">
         <v>400</v>
-      </c>
-      <c r="E7" t="n">
-        <v>400</v>
-      </c>
-      <c r="F7" t="n">
-        <v>400</v>
-      </c>
-      <c r="G7" t="n">
-        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
-        <v>322.6101351477314</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
@@ -27879,13 +27879,13 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>315.2014683330166</v>
       </c>
       <c r="V7" t="n">
         <v>400</v>
@@ -27894,10 +27894,10 @@
         <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27907,16 +27907,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
-        <v>307.3903671255648</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>400</v>
@@ -27925,40 +27925,40 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
+        <v>56.51176829727029</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>250.8785988282945</v>
+      </c>
+      <c r="S8" t="n">
         <v>400</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27976,7 +27976,7 @@
         <v>400</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -27989,10 +27989,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>250.7033677259335</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28046,16 +28046,16 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>342.2743756165772</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28065,34 +28065,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>306.429487242304</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28122,19 +28122,19 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>268.2422321982431</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28256,7 +28256,7 @@
         <v>225</v>
       </c>
       <c r="M12" t="n">
-        <v>225</v>
+        <v>19.1168712588388</v>
       </c>
       <c r="N12" t="n">
         <v>225</v>
@@ -28265,7 +28265,7 @@
         <v>225</v>
       </c>
       <c r="P12" t="n">
-        <v>19.11687125883863</v>
+        <v>225</v>
       </c>
       <c r="Q12" t="n">
         <v>225</v>
@@ -28484,22 +28484,22 @@
         <v>251</v>
       </c>
       <c r="J15" t="n">
+        <v>166.1982915220773</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>251</v>
-      </c>
-      <c r="K15" t="n">
-        <v>251</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>251</v>
       </c>
       <c r="O15" t="n">
-        <v>166.1982915220776</v>
+        <v>251</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -28724,13 +28724,13 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="L18" t="n">
         <v>155.6705902671031</v>
       </c>
       <c r="M18" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -28855,7 +28855,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>279.000000000006</v>
+        <v>279</v>
       </c>
       <c r="C20" t="n">
         <v>279</v>
@@ -28958,22 +28958,22 @@
         <v>279</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>279</v>
       </c>
-      <c r="K21" t="n">
-        <v>155.6705902671031</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>155.6705902671033</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988283643</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
         <v>279</v>
@@ -29195,25 +29195,25 @@
         <v>279</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>155.6705902671031</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>279</v>
-      </c>
-      <c r="K24" t="n">
-        <v>155.6705902671031</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>279</v>
@@ -29435,7 +29435,7 @@
         <v>225</v>
       </c>
       <c r="K27" t="n">
-        <v>19.11687125883918</v>
+        <v>225</v>
       </c>
       <c r="L27" t="n">
         <v>225</v>
@@ -29450,7 +29450,7 @@
         <v>225</v>
       </c>
       <c r="P27" t="n">
-        <v>225</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q27" t="n">
         <v>225</v>
@@ -29678,10 +29678,10 @@
         <v>225</v>
       </c>
       <c r="M30" t="n">
-        <v>19.11687125883903</v>
+        <v>225</v>
       </c>
       <c r="N30" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="O30" t="n">
         <v>225</v>
@@ -29824,7 +29824,7 @@
         <v>291</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>141.6245682972704</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>242.4220074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
         <v>291</v>
@@ -29906,28 +29906,28 @@
         <v>291</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>227.015861157829</v>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>291</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>227.0158611578291</v>
       </c>
       <c r="R33" t="n">
         <v>291</v>
@@ -29961,7 +29961,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>291</v>
+        <v>291.0000000000239</v>
       </c>
       <c r="C34" t="n">
         <v>291</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>242.4220074428797</v>
       </c>
       <c r="S35" t="n">
         <v>291</v>
@@ -30109,7 +30109,7 @@
         <v>291</v>
       </c>
       <c r="Y35" t="n">
-        <v>282.5434086145857</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36">
@@ -30143,7 +30143,7 @@
         <v>291</v>
       </c>
       <c r="J36" t="n">
-        <v>227.015861157829</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -30158,7 +30158,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>227.0158611578287</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -30298,7 +30298,7 @@
         <v>291</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>141.6245682972704</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>242.4220074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>291</v>
@@ -30386,13 +30386,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>227.0158611578289</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>227.0158611578289</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -30435,7 +30435,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>291</v>
+        <v>291.0000000000276</v>
       </c>
       <c r="C40" t="n">
         <v>291</v>
@@ -30617,7 +30617,7 @@
         <v>213</v>
       </c>
       <c r="J42" t="n">
-        <v>158.597814363541</v>
+        <v>158.5978143635411</v>
       </c>
       <c r="K42" t="n">
         <v>213</v>
@@ -30696,7 +30696,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>65.00462472645802</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30729,10 +30729,10 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U43" t="n">
-        <v>150.9583912744579</v>
+        <v>166.8643773812244</v>
       </c>
       <c r="V43" t="n">
-        <v>199.1703102162162</v>
+        <v>213</v>
       </c>
       <c r="W43" t="n">
         <v>213</v>
@@ -30860,10 +30860,10 @@
         <v>187</v>
       </c>
       <c r="L45" t="n">
-        <v>70.35302008818687</v>
+        <v>187</v>
       </c>
       <c r="M45" t="n">
-        <v>187</v>
+        <v>86.20001395581806</v>
       </c>
       <c r="N45" t="n">
         <v>187</v>
@@ -30875,7 +30875,7 @@
         <v>187</v>
       </c>
       <c r="Q45" t="n">
-        <v>173.0792650904796</v>
+        <v>187</v>
       </c>
       <c r="R45" t="n">
         <v>187</v>
@@ -30933,7 +30933,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J46" t="n">
-        <v>87.85860300887572</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -34883,7 +34883,7 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34901,7 +34901,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>208.6390057631421</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34928,7 +34928,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>189.9754334937423</v>
@@ -34937,7 +34937,7 @@
         <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>131.8017441158486</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -35120,22 +35120,22 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>145.9766795276131</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -35165,13 +35165,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>164.2430770585587</v>
       </c>
       <c r="V7" t="n">
         <v>200.8296897837838</v>
@@ -35180,10 +35180,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35220,7 +35220,7 @@
         <v>814</v>
       </c>
       <c r="K8" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
@@ -35235,10 +35235,10 @@
         <v>814</v>
       </c>
       <c r="P8" t="n">
+        <v>814.0000000000045</v>
+      </c>
+      <c r="Q8" t="n">
         <v>814</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>814.0000000000045</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,34 +35351,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>25.44858240534745</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35408,19 +35408,19 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>117.2838409237851</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35542,7 +35542,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
-        <v>311.9500421645043</v>
+        <v>106.0669134233431</v>
       </c>
       <c r="N12" t="n">
         <v>359.6265501086548</v>
@@ -35551,7 +35551,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>132.7828757734918</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
         <v>51.92073490952041</v>
@@ -35770,22 +35770,22 @@
         <v>33.87361410865147</v>
       </c>
       <c r="J15" t="n">
-        <v>376.2086062376757</v>
+        <v>291.406897759753</v>
       </c>
       <c r="K15" t="n">
-        <v>442.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
-        <v>86.95004216450428</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N15" t="n">
         <v>385.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>407.6553134248239</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P15" t="n">
         <v>113.6660045146532</v>
@@ -35928,13 +35928,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>113.7832223189554</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="L17" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,7 +35943,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -36010,13 +36010,13 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L18" t="n">
         <v>429.7619656157901</v>
       </c>
       <c r="M18" t="n">
-        <v>365.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N18" t="n">
         <v>134.6265501086548</v>
@@ -36165,13 +36165,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L20" t="n">
-        <v>814.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,13 +36180,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>556.8126112610438</v>
+        <v>532.5214919778892</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36244,10 +36244,10 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J21" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>346.7744449078945</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
         <v>274.091375348687</v>
@@ -36256,10 +36256,10 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N21" t="n">
-        <v>134.6265501086548</v>
+        <v>413.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>241.4570219027464</v>
+        <v>397.1276121698497</v>
       </c>
       <c r="P21" t="n">
         <v>113.6660045146532</v>
@@ -36405,7 +36405,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230993</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -36417,7 +36417,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>532.5214919778892</v>
+        <v>814</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -36426,7 +36426,7 @@
         <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
-        <v>6.981979528761874e-11</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36481,10 +36481,10 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J24" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>346.7744449078945</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
         <v>274.091375348687</v>
@@ -36493,13 +36493,13 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
-        <v>134.6265501086548</v>
+        <v>290.2971403757579</v>
       </c>
       <c r="O24" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>113.6660045146532</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q24" t="n">
         <v>105.9207349095204</v>
@@ -36642,10 +36642,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>772.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,7 +36654,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>314.0531751575541</v>
+        <v>370.1780576344547</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -36721,7 +36721,7 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>210.2207258996305</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
         <v>499.091375348687</v>
@@ -36736,7 +36736,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q27" t="n">
         <v>51.92073490952041</v>
@@ -36888,13 +36888,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>619.4144644189528</v>
+        <v>216.5925220533733</v>
       </c>
       <c r="O29" t="n">
-        <v>370.1780576344547</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>773.0000000000339</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -36964,10 +36964,10 @@
         <v>499.091375348687</v>
       </c>
       <c r="M30" t="n">
-        <v>106.0669134233433</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>359.6265501086548</v>
+        <v>153.743421367494</v>
       </c>
       <c r="O30" t="n">
         <v>466.4570219027464</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="K32" t="n">
+        <v>727.1079320762516</v>
+      </c>
+      <c r="L32" t="n">
         <v>772.9999999999999</v>
       </c>
-      <c r="L32" t="n">
-        <v>727.1079320760621</v>
-      </c>
       <c r="M32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="O32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="Q32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37192,10 +37192,10 @@
         <v>73.87361410865147</v>
       </c>
       <c r="J33" t="n">
-        <v>125.2086062376757</v>
+        <v>352.2244673955047</v>
       </c>
       <c r="K33" t="n">
-        <v>482.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
         <v>274.091375348687</v>
@@ -37213,7 +37213,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>53.93659606734953</v>
+        <v>117.9207349095204</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37247,7 +37247,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.886199662921342</v>
+        <v>3.886199662945266</v>
       </c>
       <c r="C34" t="n">
         <v>18.27475335195533</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="K35" t="n">
+        <v>727.1079320759604</v>
+      </c>
+      <c r="L35" t="n">
         <v>773</v>
       </c>
-      <c r="L35" t="n">
-        <v>727.1079320759791</v>
-      </c>
       <c r="M35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="P35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="Q35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37429,7 +37429,7 @@
         <v>73.87361410865147</v>
       </c>
       <c r="J36" t="n">
-        <v>352.2244673955047</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K36" t="n">
         <v>191.1038546407913</v>
@@ -37444,7 +37444,7 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O36" t="n">
-        <v>241.4570219027464</v>
+        <v>468.4728830605751</v>
       </c>
       <c r="P36" t="n">
         <v>113.6660045146532</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320759591</v>
+        <v>727.1079320761845</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>773.0000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="N38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="P38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="Q38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37672,13 +37672,13 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L39" t="n">
-        <v>274.091375348687</v>
+        <v>501.1072365065158</v>
       </c>
       <c r="M39" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N39" t="n">
-        <v>361.6424112664837</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O39" t="n">
         <v>241.4570219027464</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.886199662921342</v>
+        <v>3.886199662948904</v>
       </c>
       <c r="C40" t="n">
         <v>18.27475335195533</v>
@@ -37903,7 +37903,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>283.8064206012167</v>
+        <v>283.8064206012168</v>
       </c>
       <c r="K42" t="n">
         <v>404.1038546407913</v>
@@ -37982,7 +37982,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>29.73567589055027</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38015,10 +38015,10 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>15.90598610676645</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>13.82968978378381</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -38061,13 +38061,13 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>765.4397879755212</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38076,7 +38076,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>370.1780576344547</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -38146,10 +38146,10 @@
         <v>378.1038546407913</v>
       </c>
       <c r="L45" t="n">
-        <v>344.4443954368738</v>
+        <v>461.091375348687</v>
       </c>
       <c r="M45" t="n">
-        <v>273.9500421645043</v>
+        <v>173.1500561203223</v>
       </c>
       <c r="N45" t="n">
         <v>321.6265501086548</v>
@@ -38161,7 +38161,7 @@
         <v>300.6660045146532</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>13.92073490952041</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>52.58965417296794</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
